--- a/paper simu/interval_counts.xlsx
+++ b/paper simu/interval_counts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baptiste\Documents\PhD\Projects\RL_CS\paper simu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711481BA-B03F-454C-807F-7FE10249E523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9896FC-4A79-4CF0-B5FB-F896935E8659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB71E39A-EF66-48CE-B2F2-5735E1E7A096}"/>
   </bookViews>
@@ -50,23 +50,22 @@
     <t>quintuplets</t>
   </si>
   <si>
-    <t>(0,0.015]</t>
+    <t>(0,σ]</t>
   </si>
   <si>
-    <t>(0.015,0.03]</t>
+    <t>(σ,2σ]</t>
   </si>
   <si>
-    <t>0
-Optimum</t>
+    <t>(2σ,4σ]</t>
   </si>
   <si>
-    <t>(0.03,0.045]</t>
+    <t>(4σ,6σ]</t>
   </si>
   <si>
-    <t>(0.045,0.06]</t>
+    <t>(6σ,∞)</t>
   </si>
   <si>
-    <t>(0.06,0.08]</t>
+    <t>Optimum</t>
   </si>
 </sst>
 </file>
@@ -627,9 +626,88 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+              </a:rPr>
+              <a:t>(a) Annealing</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16624291322741691"/>
+          <c:y val="8.115281952070523E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14948239490786142"/>
+          <c:y val="6.5010101010101018E-2"/>
+          <c:w val="0.82198343934005391"/>
+          <c:h val="0.73308319227417951"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -637,63 +715,73 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>interval_counts!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>annealing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>interval_counts!$A$9:$A$14</c:f>
+              <c:f>interval_counts!$A$11:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0
-Optimum</c:v>
+                  <c:v>Optimum</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>(0,0.015]</c:v>
+                  <c:v>(0,σ]</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>(0.015,0.03]</c:v>
+                  <c:v>(σ,2σ]</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>(0.03,0.045]</c:v>
+                  <c:v>(2σ,4σ]</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>(0.045,0.06]</c:v>
+                  <c:v>(4σ,6σ]</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>(0.06,0.08]</c:v>
+                  <c:v>(6σ,∞)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>interval_counts!$B$9:$B$14</c:f>
+              <c:f>interval_counts!$B$11:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>53.08</c:v>
+                  <c:v>45.78</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36.880000000000003</c:v>
+                  <c:v>25.12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.1</c:v>
+                  <c:v>17.88</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.94</c:v>
+                  <c:v>10.34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.88</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -703,7 +791,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6AC7-4ACE-9C25-458F5E4DDFF4}"/>
+              <c16:uniqueId val="{00000000-EE81-43CF-9D4B-954BC5DA7537}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -717,11 +805,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="2135975711"/>
-        <c:axId val="2135992511"/>
+        <c:axId val="319415039"/>
+        <c:axId val="319415999"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2135975711"/>
+        <c:axId val="319415039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -741,23 +829,49 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Estimate</a:t>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t>Distance to </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> distance to the optimum</a:t>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t>optimum</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-US" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.38703945437723386"/>
+              <c:y val="0.91291051385729827"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -778,9 +892,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -809,22 +923,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2135992511"/>
+        <c:crossAx val="319415999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -832,10 +943,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2135992511"/>
+        <c:axId val="319415999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -843,9 +955,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -862,31 +973,34 @@
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Percentage of estimates within given</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>distance</a:t>
+                  <a:rPr lang="en-US" sz="1200" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t>Frequency (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.3626085200888362E-3"/>
+              <c:y val="0.31974074074074071"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -902,14 +1016,11 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -932,29 +1043,28 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:ea typeface="ADLaM Display" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2135975711"/>
+        <c:crossAx val="319415039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -975,12 +1085,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -998,7 +1103,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -1010,16 +1115,95 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="104"/>
+      <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="4"/>
+      <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+              </a:rPr>
+              <a:t>(b) Random</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16624291322741691"/>
+          <c:y val="8.115281952070523E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14948239490786142"/>
+          <c:y val="6.5010101010101018E-2"/>
+          <c:w val="0.82198343934005391"/>
+          <c:h val="0.73308319227417951"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1027,73 +1211,83 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>interval_counts!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>random</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>interval_counts!$A$9:$A$14</c:f>
+              <c:f>interval_counts!$A$11:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0
-Optimum</c:v>
+                  <c:v>Optimum</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>(0,0.015]</c:v>
+                  <c:v>(0,σ]</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>(0.015,0.03]</c:v>
+                  <c:v>(σ,2σ]</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>(0.03,0.045]</c:v>
+                  <c:v>(2σ,4σ]</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>(0.045,0.06]</c:v>
+                  <c:v>(4σ,6σ]</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>(0.06,0.08]</c:v>
+                  <c:v>(6σ,∞)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>interval_counts!$C$9:$C$14</c:f>
+              <c:f>interval_counts!$C$11:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>21.32</c:v>
+                  <c:v>6.08</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.06</c:v>
+                  <c:v>11.42</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.38</c:v>
+                  <c:v>21.86</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22.24</c:v>
+                  <c:v>37.159999999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>22.04</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1.44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-72D2-4EAC-A507-E18CCD7134B5}"/>
+              <c16:uniqueId val="{00000000-63CA-4EAB-82BB-630AC3B9871A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1107,11 +1301,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="2135999231"/>
-        <c:axId val="2135999711"/>
+        <c:axId val="319415039"/>
+        <c:axId val="319415999"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2135999231"/>
+        <c:axId val="319415039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1123,47 +1317,40 @@
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-                  <a:lnSpc>
-                    <a:spcPct val="100000"/>
-                  </a:lnSpc>
-                  <a:spcBef>
-                    <a:spcPts val="0"/>
-                  </a:spcBef>
-                  <a:spcAft>
-                    <a:spcPts val="0"/>
-                  </a:spcAft>
-                  <a:buClrTx/>
-                  <a:buSzTx/>
-                  <a:buFontTx/>
-                  <a:buNone/>
-                  <a:tabLst/>
+                <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
+                      <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
                         <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Estimate distance to the optimum</a:t>
+                  <a:t>Distance to optimum</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.39203211182923703"/>
+              <c:y val="0.91677854515728574"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1176,31 +1363,17 @@
             <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-                <a:lnSpc>
-                  <a:spcPct val="100000"/>
-                </a:lnSpc>
-                <a:spcBef>
-                  <a:spcPts val="0"/>
-                </a:spcBef>
-                <a:spcAft>
-                  <a:spcPts val="0"/>
-                </a:spcAft>
-                <a:buClrTx/>
-                <a:buSzTx/>
-                <a:buFontTx/>
-                <a:buNone/>
-                <a:tabLst/>
+              <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000">
+                    <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
                       <a:lumOff val="35000"/>
-                    </a:sysClr>
+                    </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1229,22 +1402,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2135999711"/>
+        <c:crossAx val="319415999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1252,10 +1422,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2135999711"/>
+        <c:axId val="319415999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1263,9 +1434,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1282,30 +1452,34 @@
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Percentage of estimates within given distance</a:t>
+                  <a:t>Frequency (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.3626085200888362E-3"/>
+              <c:y val="0.31974074074074071"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1321,14 +1495,11 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1351,29 +1522,28 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:ea typeface="ADLaM Display" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2135999231"/>
+        <c:crossAx val="319415039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -1394,12 +1564,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1417,7 +1582,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -1429,16 +1594,95 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="105"/>
+      <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="5"/>
+      <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+              </a:rPr>
+              <a:t>(c) Quadruplets sketch</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17373189940542166"/>
+          <c:y val="8.115281952070523E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14948239490786142"/>
+          <c:y val="6.5010101010101018E-2"/>
+          <c:w val="0.82198343934005391"/>
+          <c:h val="0.73308319227417951"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1446,63 +1690,73 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>interval_counts!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quadruplets</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>interval_counts!$A$9:$A$14</c:f>
+              <c:f>interval_counts!$A$11:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0
-Optimum</c:v>
+                  <c:v>Optimum</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>(0,0.015]</c:v>
+                  <c:v>(0,σ]</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>(0.015,0.03]</c:v>
+                  <c:v>(σ,2σ]</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>(0.03,0.045]</c:v>
+                  <c:v>(2σ,4σ]</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>(0.045,0.06]</c:v>
+                  <c:v>(4σ,6σ]</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>(0.06,0.08]</c:v>
+                  <c:v>(6σ,∞)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>interval_counts!$D$9:$D$14</c:f>
+              <c:f>interval_counts!$D$11:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>49.66</c:v>
+                  <c:v>57.56</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33.82</c:v>
+                  <c:v>29.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.54</c:v>
+                  <c:v>10.36</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.98</c:v>
+                  <c:v>2.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.46</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -1512,7 +1766,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C8AC-4AA6-8638-F93DEB4D23D4}"/>
+              <c16:uniqueId val="{00000000-E39A-449F-BB84-0EA2F66FC48B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1526,11 +1780,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="308108255"/>
-        <c:axId val="308111615"/>
+        <c:axId val="319415039"/>
+        <c:axId val="319415999"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="308108255"/>
+        <c:axId val="319415039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1550,25 +1804,32 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Estimate distance to the optimum</a:t>
+                  <a:t>Distance to optimum</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.3945284405552385"/>
+              <c:y val="0.92064657645727321"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1589,9 +1850,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1620,22 +1881,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="308111615"/>
+        <c:crossAx val="319415999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1643,10 +1901,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="308111615"/>
+        <c:axId val="319415999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1654,9 +1913,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1673,30 +1931,34 @@
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Percentage of estimates within given distance</a:t>
+                  <a:t>Frequency (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.3626085200888362E-3"/>
+              <c:y val="0.31974074074074071"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1712,14 +1974,11 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1742,29 +2001,28 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:ea typeface="ADLaM Display" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="308108255"/>
+        <c:crossAx val="319415039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -1785,12 +2043,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1808,7 +2061,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -1827,9 +2080,88 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+              </a:rPr>
+              <a:t>(d) Quintuplets sketch</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17373189940542166"/>
+          <c:y val="8.115281952070523E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14948239490786142"/>
+          <c:y val="6.5010101010101018E-2"/>
+          <c:w val="0.82198343934005391"/>
+          <c:h val="0.73308319227417951"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1837,73 +2169,83 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>interval_counts!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>quintuplets</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="00B0F0"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>interval_counts!$A$9:$A$14</c:f>
+              <c:f>interval_counts!$A$11:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0
-Optimum</c:v>
+                  <c:v>Optimum</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>(0,0.015]</c:v>
+                  <c:v>(0,σ]</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>(0.015,0.03]</c:v>
+                  <c:v>(σ,2σ]</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>(0.03,0.045]</c:v>
+                  <c:v>(2σ,4σ]</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>(0.045,0.06]</c:v>
+                  <c:v>(4σ,6σ]</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>(0.06,0.08]</c:v>
+                  <c:v>(6σ,∞)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>interval_counts!$E$9:$E$14</c:f>
+              <c:f>interval_counts!$E$11:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>63.48</c:v>
+                  <c:v>48.92</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30.54</c:v>
+                  <c:v>30.36</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.5</c:v>
+                  <c:v>13.68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.48</c:v>
+                  <c:v>5.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FA27-47F3-B763-8E96F0067F33}"/>
+              <c16:uniqueId val="{00000000-9F98-4F33-9649-7DE490F1899D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1917,11 +2259,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="63855711"/>
-        <c:axId val="63856191"/>
+        <c:axId val="319415039"/>
+        <c:axId val="319415999"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="63855711"/>
+        <c:axId val="319415039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1941,25 +2283,32 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Estimate distance to the optimum</a:t>
+                  <a:t>Distance to optimum</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.39203211182923692"/>
+              <c:y val="0.92064657645727321"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1980,9 +2329,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -2011,22 +2360,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63856191"/>
+        <c:crossAx val="319415999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2034,10 +2380,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63856191"/>
+        <c:axId val="319415999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2045,9 +2392,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -2064,30 +2410,34 @@
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1200" b="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:rPr>
-                  <a:t>Percentage of estimates within given distance</a:t>
+                  <a:t>Frequency (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.3626085200888362E-3"/>
+              <c:y val="0.31974074074074071"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2103,14 +2453,11 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman10" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -2133,29 +2480,28 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                <a:ea typeface="ADLaM Display" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63855711"/>
+        <c:crossAx val="319415039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -2176,12 +2522,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -2199,7 +2540,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -2245,14 +2586,82 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -4312,27 +4721,29 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>582706</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>376236</xdr:rowOff>
+      <xdr:rowOff>44823</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>224118</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>89647</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02505301-62AB-CB9A-401A-DEC2FF9E73C4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32047A8E-8244-4C68-A835-C628C9EFD8D7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4349,26 +4760,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:colOff>593912</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>67235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>235324</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A835D2AD-D1B5-B1BE-1600-16D0D79C46A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA9A629A-617A-43CB-9700-A5C9BE85048C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4385,26 +4798,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>4761</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>246530</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7">
+        <xdr:cNvPr id="10" name="Chart 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1211C504-60F1-B965-FA15-AB1205ACF1CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{225435A3-AE5F-4E21-80C9-BD74A7467EF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4420,27 +4835,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>600074</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>4481</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>246530</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Chart 8">
+        <xdr:cNvPr id="11" name="Chart 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D407A6A-DEF1-4605-1770-3D02E032295F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FDE374E-ABC1-4151-B5B3-48AC91EECAB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4774,7 +5191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50CE8FF9-6411-4D75-853F-EB0C55196DCA}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -4797,21 +5214,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>2654</v>
+        <v>2289</v>
       </c>
       <c r="C2">
-        <v>1066</v>
+        <v>304</v>
       </c>
       <c r="D2">
-        <v>2483</v>
+        <v>2878</v>
       </c>
       <c r="E2">
-        <v>3174</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4819,16 +5236,16 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>1844</v>
+        <v>1256</v>
       </c>
       <c r="C3">
-        <v>1553</v>
+        <v>571</v>
       </c>
       <c r="D3">
-        <v>1691</v>
+        <v>1460</v>
       </c>
       <c r="E3">
-        <v>1527</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4836,193 +5253,193 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>405</v>
+        <v>894</v>
       </c>
       <c r="C4">
-        <v>1269</v>
+        <v>1093</v>
       </c>
       <c r="D4">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="E4">
-        <v>225</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>97</v>
+        <v>517</v>
       </c>
       <c r="C5">
-        <v>1112</v>
+        <v>1858</v>
       </c>
       <c r="D5">
-        <v>299</v>
+        <v>121</v>
       </c>
       <c r="E5">
-        <v>74</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <f>B2/50</f>
-        <v>53.08</v>
-      </c>
-      <c r="C9">
-        <f t="shared" ref="C9:E9" si="0">C2/50</f>
-        <v>21.32</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>49.66</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>63.48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <f t="shared" ref="B10:E14" si="1">B3/50</f>
-        <v>36.880000000000003</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="1"/>
-        <v>31.06</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="1"/>
-        <v>33.82</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="1"/>
-        <v>30.54</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>6</v>
+      <c r="A11" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B11">
-        <f t="shared" si="1"/>
-        <v>8.1</v>
+        <f t="shared" ref="B11:E16" si="0">B2/50</f>
+        <v>45.78</v>
       </c>
       <c r="C11">
-        <f t="shared" si="1"/>
-        <v>25.38</v>
+        <f t="shared" si="0"/>
+        <v>6.08</v>
       </c>
       <c r="D11">
-        <f t="shared" si="1"/>
-        <v>10.54</v>
+        <f t="shared" si="0"/>
+        <v>57.56</v>
       </c>
       <c r="E11">
-        <f t="shared" si="1"/>
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>48.92</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B12">
-        <f t="shared" si="1"/>
-        <v>1.94</v>
+        <f t="shared" si="0"/>
+        <v>25.12</v>
       </c>
       <c r="C12">
-        <f t="shared" si="1"/>
-        <v>22.24</v>
+        <f t="shared" si="0"/>
+        <v>11.42</v>
       </c>
       <c r="D12">
-        <f t="shared" si="1"/>
-        <v>5.98</v>
+        <f t="shared" si="0"/>
+        <v>29.2</v>
       </c>
       <c r="E12">
-        <f t="shared" si="1"/>
-        <v>1.48</v>
+        <f t="shared" si="0"/>
+        <v>30.36</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>17.88</v>
       </c>
       <c r="C13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>21.86</v>
       </c>
       <c r="D13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>10.36</v>
       </c>
       <c r="E13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>13.68</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
+        <v>10.34</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>37.159999999999997</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>2.42</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0.88</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>22.04</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>0.46</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14">
-        <f t="shared" si="1"/>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>1.44</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
